--- a/media/Levels/levels.xlsx
+++ b/media/Levels/levels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{821A4AC2-0451-43E5-9146-4F8A24A23795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F290A4-FB40-4EA7-A9D6-859BD26803EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
   </bookViews>
@@ -3192,23 +3192,23 @@
       <c r="CX5">
         <v>12</v>
       </c>
-      <c r="CY5" s="3">
-        <v>0</v>
-      </c>
-      <c r="CZ5" s="3">
-        <v>0</v>
-      </c>
-      <c r="DA5" s="3">
-        <v>0</v>
-      </c>
-      <c r="DB5" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC5" s="3">
-        <v>0</v>
+      <c r="CY5">
+        <v>12</v>
+      </c>
+      <c r="CZ5">
+        <v>12</v>
+      </c>
+      <c r="DA5">
+        <v>12</v>
+      </c>
+      <c r="DB5">
+        <v>12</v>
+      </c>
+      <c r="DC5">
+        <v>12</v>
       </c>
       <c r="DD5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="DE5">
         <v>12</v>
@@ -3644,38 +3644,38 @@
       <c r="CX6">
         <v>12</v>
       </c>
-      <c r="CY6" s="3">
-        <v>0</v>
-      </c>
-      <c r="CZ6" s="3">
-        <v>0</v>
-      </c>
-      <c r="DA6" s="3">
-        <v>0</v>
-      </c>
-      <c r="DB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC6" s="3">
-        <v>0</v>
+      <c r="CY6">
+        <v>12</v>
+      </c>
+      <c r="CZ6">
+        <v>12</v>
+      </c>
+      <c r="DA6">
+        <v>12</v>
+      </c>
+      <c r="DB6">
+        <v>12</v>
+      </c>
+      <c r="DC6">
+        <v>12</v>
       </c>
       <c r="DD6">
-        <v>0</v>
-      </c>
-      <c r="DE6">
-        <v>12</v>
-      </c>
-      <c r="DF6">
-        <v>12</v>
-      </c>
-      <c r="DG6">
-        <v>12</v>
-      </c>
-      <c r="DH6">
-        <v>12</v>
-      </c>
-      <c r="DI6">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="DE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG6" s="3">
+        <v>0</v>
+      </c>
+      <c r="DH6" s="3">
+        <v>0</v>
+      </c>
+      <c r="DI6" s="3">
+        <v>0</v>
       </c>
       <c r="DJ6">
         <v>12</v>
@@ -4096,32 +4096,32 @@
       <c r="CX7">
         <v>12</v>
       </c>
-      <c r="CY7" s="3">
-        <v>0</v>
-      </c>
-      <c r="CZ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="DA7" s="3">
-        <v>8</v>
-      </c>
-      <c r="DB7" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC7" s="3">
-        <v>0</v>
+      <c r="CY7">
+        <v>12</v>
+      </c>
+      <c r="CZ7">
+        <v>12</v>
+      </c>
+      <c r="DA7">
+        <v>12</v>
+      </c>
+      <c r="DB7">
+        <v>12</v>
+      </c>
+      <c r="DC7">
+        <v>12</v>
       </c>
       <c r="DD7">
-        <v>0</v>
-      </c>
-      <c r="DE7">
-        <v>12</v>
-      </c>
-      <c r="DF7">
-        <v>12</v>
-      </c>
-      <c r="DG7">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="DE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG7" s="3">
+        <v>0</v>
       </c>
       <c r="DH7" s="3">
         <v>0</v>
@@ -4129,14 +4129,14 @@
       <c r="DI7" s="3">
         <v>0</v>
       </c>
-      <c r="DJ7" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK7" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL7" s="3">
-        <v>0</v>
+      <c r="DJ7">
+        <v>12</v>
+      </c>
+      <c r="DK7">
+        <v>12</v>
+      </c>
+      <c r="DL7">
+        <v>12</v>
       </c>
       <c r="DM7">
         <v>12</v>
@@ -4482,8 +4482,8 @@
       <c r="CB8">
         <v>12</v>
       </c>
-      <c r="CC8">
-        <v>12</v>
+      <c r="CC8" s="2">
+        <v>0</v>
       </c>
       <c r="CD8" s="2">
         <v>0</v>
@@ -4542,38 +4542,38 @@
       <c r="CV8" s="2">
         <v>0</v>
       </c>
-      <c r="CW8" s="2">
-        <v>0</v>
+      <c r="CW8">
+        <v>12</v>
       </c>
       <c r="CX8">
         <v>12</v>
       </c>
-      <c r="CY8" s="3">
-        <v>0</v>
-      </c>
-      <c r="CZ8" s="3">
-        <v>0</v>
-      </c>
-      <c r="DA8" s="3">
-        <v>0</v>
-      </c>
-      <c r="DB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC8" s="3">
-        <v>0</v>
+      <c r="CY8">
+        <v>12</v>
+      </c>
+      <c r="CZ8">
+        <v>12</v>
+      </c>
+      <c r="DA8">
+        <v>12</v>
+      </c>
+      <c r="DB8">
+        <v>12</v>
+      </c>
+      <c r="DC8">
+        <v>12</v>
       </c>
       <c r="DD8">
-        <v>0</v>
-      </c>
-      <c r="DE8">
-        <v>12</v>
-      </c>
-      <c r="DF8">
-        <v>12</v>
-      </c>
-      <c r="DG8">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="DE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG8" s="3">
+        <v>8</v>
       </c>
       <c r="DH8" s="3">
         <v>0</v>
@@ -4581,14 +4581,14 @@
       <c r="DI8" s="3">
         <v>0</v>
       </c>
-      <c r="DJ8" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK8" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL8" s="3">
-        <v>0</v>
+      <c r="DJ8">
+        <v>12</v>
+      </c>
+      <c r="DK8">
+        <v>12</v>
+      </c>
+      <c r="DL8">
+        <v>12</v>
       </c>
       <c r="DM8">
         <v>12</v>
@@ -4934,8 +4934,8 @@
       <c r="CB9">
         <v>12</v>
       </c>
-      <c r="CC9">
-        <v>12</v>
+      <c r="CC9" s="2">
+        <v>0</v>
       </c>
       <c r="CD9" s="2">
         <v>0</v>
@@ -4994,38 +4994,38 @@
       <c r="CV9" s="2">
         <v>0</v>
       </c>
-      <c r="CW9" s="2">
-        <v>0</v>
+      <c r="CW9">
+        <v>12</v>
       </c>
       <c r="CX9">
         <v>12</v>
       </c>
-      <c r="CY9" s="3">
-        <v>0</v>
-      </c>
-      <c r="CZ9" s="3">
-        <v>0</v>
-      </c>
-      <c r="DA9" s="3">
-        <v>0</v>
-      </c>
-      <c r="DB9" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC9" s="3">
-        <v>0</v>
+      <c r="CY9">
+        <v>12</v>
+      </c>
+      <c r="CZ9">
+        <v>12</v>
+      </c>
+      <c r="DA9">
+        <v>12</v>
+      </c>
+      <c r="DB9">
+        <v>12</v>
+      </c>
+      <c r="DC9">
+        <v>12</v>
       </c>
       <c r="DD9">
-        <v>0</v>
-      </c>
-      <c r="DE9">
-        <v>12</v>
-      </c>
-      <c r="DF9">
-        <v>12</v>
-      </c>
-      <c r="DG9">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="DE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG9" s="3">
+        <v>0</v>
       </c>
       <c r="DH9" s="3">
         <v>0</v>
@@ -5033,14 +5033,14 @@
       <c r="DI9" s="3">
         <v>0</v>
       </c>
-      <c r="DJ9" s="3">
-        <v>8</v>
-      </c>
-      <c r="DK9" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL9" s="3">
-        <v>0</v>
+      <c r="DJ9">
+        <v>12</v>
+      </c>
+      <c r="DK9">
+        <v>12</v>
+      </c>
+      <c r="DL9">
+        <v>12</v>
       </c>
       <c r="DM9">
         <v>12</v>
@@ -5386,8 +5386,8 @@
       <c r="CB10">
         <v>12</v>
       </c>
-      <c r="CC10">
-        <v>12</v>
+      <c r="CC10" s="2">
+        <v>0</v>
       </c>
       <c r="CD10" s="2">
         <v>0</v>
@@ -5446,8 +5446,8 @@
       <c r="CV10" s="2">
         <v>0</v>
       </c>
-      <c r="CW10" s="2">
-        <v>0</v>
+      <c r="CW10">
+        <v>12</v>
       </c>
       <c r="CX10">
         <v>12</v>
@@ -5470,14 +5470,14 @@
       <c r="DD10">
         <v>12</v>
       </c>
-      <c r="DE10">
-        <v>12</v>
-      </c>
-      <c r="DF10">
-        <v>12</v>
-      </c>
-      <c r="DG10">
-        <v>12</v>
+      <c r="DE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG10" s="3">
+        <v>0</v>
       </c>
       <c r="DH10" s="3">
         <v>0</v>
@@ -5485,14 +5485,14 @@
       <c r="DI10" s="3">
         <v>0</v>
       </c>
-      <c r="DJ10" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK10" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL10" s="3">
-        <v>0</v>
+      <c r="DJ10">
+        <v>12</v>
+      </c>
+      <c r="DK10">
+        <v>12</v>
+      </c>
+      <c r="DL10">
+        <v>12</v>
       </c>
       <c r="DM10">
         <v>12</v>
@@ -5838,8 +5838,8 @@
       <c r="CB11">
         <v>12</v>
       </c>
-      <c r="CC11">
-        <v>12</v>
+      <c r="CC11" s="2">
+        <v>0</v>
       </c>
       <c r="CD11" s="2">
         <v>0</v>
@@ -5898,8 +5898,8 @@
       <c r="CV11" s="2">
         <v>0</v>
       </c>
-      <c r="CW11" s="2">
-        <v>0</v>
+      <c r="CW11">
+        <v>12</v>
       </c>
       <c r="CX11">
         <v>12</v>
@@ -5931,20 +5931,20 @@
       <c r="DG11">
         <v>12</v>
       </c>
-      <c r="DH11" s="3">
-        <v>0</v>
-      </c>
-      <c r="DI11" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ11" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK11" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL11" s="3">
-        <v>0</v>
+      <c r="DH11">
+        <v>12</v>
+      </c>
+      <c r="DI11">
+        <v>12</v>
+      </c>
+      <c r="DJ11">
+        <v>12</v>
+      </c>
+      <c r="DK11">
+        <v>12</v>
+      </c>
+      <c r="DL11">
+        <v>12</v>
       </c>
       <c r="DM11">
         <v>12</v>
@@ -6290,8 +6290,8 @@
       <c r="CB12">
         <v>12</v>
       </c>
-      <c r="CC12">
-        <v>12</v>
+      <c r="CC12" s="2">
+        <v>0</v>
       </c>
       <c r="CD12" s="2">
         <v>0</v>
@@ -6350,8 +6350,8 @@
       <c r="CV12" s="2">
         <v>0</v>
       </c>
-      <c r="CW12" s="2">
-        <v>0</v>
+      <c r="CW12">
+        <v>12</v>
       </c>
       <c r="CX12">
         <v>12</v>
@@ -6742,8 +6742,8 @@
       <c r="CB13">
         <v>12</v>
       </c>
-      <c r="CC13">
-        <v>12</v>
+      <c r="CC13" s="2">
+        <v>0</v>
       </c>
       <c r="CD13" s="2">
         <v>0</v>
@@ -6802,8 +6802,8 @@
       <c r="CV13" s="2">
         <v>0</v>
       </c>
-      <c r="CW13" s="2">
-        <v>0</v>
+      <c r="CW13">
+        <v>12</v>
       </c>
       <c r="CX13">
         <v>12</v>
@@ -7194,8 +7194,8 @@
       <c r="CB14">
         <v>12</v>
       </c>
-      <c r="CC14">
-        <v>12</v>
+      <c r="CC14" s="2">
+        <v>0</v>
       </c>
       <c r="CD14" s="2">
         <v>0</v>
@@ -7254,11 +7254,11 @@
       <c r="CV14" s="2">
         <v>0</v>
       </c>
-      <c r="CW14" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX14" s="5">
-        <v>0</v>
+      <c r="CW14">
+        <v>12</v>
+      </c>
+      <c r="CX14">
+        <v>12</v>
       </c>
       <c r="CY14">
         <v>12</v>
@@ -7314,8 +7314,8 @@
       <c r="DP14">
         <v>12</v>
       </c>
-      <c r="DQ14" s="5">
-        <v>0</v>
+      <c r="DQ14">
+        <v>12</v>
       </c>
       <c r="DR14" s="2">
         <v>0</v>
@@ -7646,8 +7646,8 @@
       <c r="CB15">
         <v>12</v>
       </c>
-      <c r="CC15">
-        <v>12</v>
+      <c r="CC15" s="2">
+        <v>0</v>
       </c>
       <c r="CD15" s="2">
         <v>0</v>
@@ -7706,14 +7706,14 @@
       <c r="CV15" s="2">
         <v>0</v>
       </c>
-      <c r="CW15" s="2">
-        <v>0</v>
+      <c r="CW15">
+        <v>12</v>
       </c>
       <c r="CX15">
         <v>12</v>
       </c>
-      <c r="CY15" s="4">
-        <v>7</v>
+      <c r="CY15">
+        <v>12</v>
       </c>
       <c r="CZ15">
         <v>12</v>
@@ -7721,20 +7721,20 @@
       <c r="DA15">
         <v>12</v>
       </c>
-      <c r="DB15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DE15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DF15" s="3">
-        <v>0</v>
+      <c r="DB15">
+        <v>12</v>
+      </c>
+      <c r="DC15">
+        <v>12</v>
+      </c>
+      <c r="DD15">
+        <v>12</v>
+      </c>
+      <c r="DE15">
+        <v>12</v>
+      </c>
+      <c r="DF15">
+        <v>12</v>
       </c>
       <c r="DG15">
         <v>12</v>
@@ -7742,20 +7742,20 @@
       <c r="DH15">
         <v>12</v>
       </c>
-      <c r="DI15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL15" s="3">
-        <v>0</v>
-      </c>
-      <c r="DM15" s="3">
-        <v>0</v>
+      <c r="DI15">
+        <v>12</v>
+      </c>
+      <c r="DJ15">
+        <v>12</v>
+      </c>
+      <c r="DK15">
+        <v>12</v>
+      </c>
+      <c r="DL15">
+        <v>12</v>
+      </c>
+      <c r="DM15">
+        <v>12</v>
       </c>
       <c r="DN15">
         <v>12</v>
@@ -7763,8 +7763,8 @@
       <c r="DO15">
         <v>12</v>
       </c>
-      <c r="DP15" s="4">
-        <v>6</v>
+      <c r="DP15">
+        <v>12</v>
       </c>
       <c r="DQ15">
         <v>12</v>
@@ -8098,8 +8098,8 @@
       <c r="CB16">
         <v>12</v>
       </c>
-      <c r="CC16">
-        <v>12</v>
+      <c r="CC16" s="2">
+        <v>0</v>
       </c>
       <c r="CD16" s="2">
         <v>0</v>
@@ -8158,8 +8158,8 @@
       <c r="CV16" s="2">
         <v>0</v>
       </c>
-      <c r="CW16" s="2">
-        <v>0</v>
+      <c r="CW16">
+        <v>12</v>
       </c>
       <c r="CX16">
         <v>12</v>
@@ -8167,26 +8167,26 @@
       <c r="CY16">
         <v>12</v>
       </c>
-      <c r="CZ16" s="5">
-        <v>0</v>
+      <c r="CZ16">
+        <v>12</v>
       </c>
       <c r="DA16">
         <v>12</v>
       </c>
-      <c r="DB16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DE16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DF16" s="3">
-        <v>0</v>
+      <c r="DB16">
+        <v>12</v>
+      </c>
+      <c r="DC16">
+        <v>12</v>
+      </c>
+      <c r="DD16">
+        <v>12</v>
+      </c>
+      <c r="DE16">
+        <v>12</v>
+      </c>
+      <c r="DF16">
+        <v>12</v>
       </c>
       <c r="DG16">
         <v>12</v>
@@ -8194,26 +8194,26 @@
       <c r="DH16">
         <v>12</v>
       </c>
-      <c r="DI16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL16" s="3">
-        <v>0</v>
-      </c>
-      <c r="DM16" s="3">
-        <v>0</v>
+      <c r="DI16">
+        <v>12</v>
+      </c>
+      <c r="DJ16">
+        <v>12</v>
+      </c>
+      <c r="DK16">
+        <v>12</v>
+      </c>
+      <c r="DL16">
+        <v>12</v>
+      </c>
+      <c r="DM16">
+        <v>12</v>
       </c>
       <c r="DN16">
         <v>12</v>
       </c>
-      <c r="DO16" s="5">
-        <v>0</v>
+      <c r="DO16">
+        <v>12</v>
       </c>
       <c r="DP16">
         <v>12</v>
@@ -8550,8 +8550,8 @@
       <c r="CB17">
         <v>12</v>
       </c>
-      <c r="CC17">
-        <v>12</v>
+      <c r="CC17" s="2">
+        <v>0</v>
       </c>
       <c r="CD17" s="2">
         <v>0</v>
@@ -8581,10 +8581,10 @@
         <v>0</v>
       </c>
       <c r="CM17" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CN17" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CO17" s="2">
         <v>0</v>
@@ -8610,8 +8610,8 @@
       <c r="CV17" s="2">
         <v>0</v>
       </c>
-      <c r="CW17" s="2">
-        <v>0</v>
+      <c r="CW17">
+        <v>12</v>
       </c>
       <c r="CX17">
         <v>12</v>
@@ -8622,23 +8622,23 @@
       <c r="CZ17">
         <v>12</v>
       </c>
-      <c r="DA17" s="4">
-        <v>7</v>
-      </c>
-      <c r="DB17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD17" s="3">
-        <v>8</v>
-      </c>
-      <c r="DE17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DF17" s="3">
-        <v>0</v>
+      <c r="DA17">
+        <v>12</v>
+      </c>
+      <c r="DB17">
+        <v>12</v>
+      </c>
+      <c r="DC17">
+        <v>12</v>
+      </c>
+      <c r="DD17">
+        <v>12</v>
+      </c>
+      <c r="DE17">
+        <v>12</v>
+      </c>
+      <c r="DF17">
+        <v>12</v>
       </c>
       <c r="DG17">
         <v>12</v>
@@ -8646,23 +8646,23 @@
       <c r="DH17">
         <v>12</v>
       </c>
-      <c r="DI17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK17" s="3">
-        <v>8</v>
-      </c>
-      <c r="DL17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DM17" s="3">
-        <v>0</v>
-      </c>
-      <c r="DN17" s="4">
-        <v>6</v>
+      <c r="DI17">
+        <v>12</v>
+      </c>
+      <c r="DJ17">
+        <v>12</v>
+      </c>
+      <c r="DK17">
+        <v>12</v>
+      </c>
+      <c r="DL17">
+        <v>12</v>
+      </c>
+      <c r="DM17">
+        <v>12</v>
+      </c>
+      <c r="DN17">
+        <v>12</v>
       </c>
       <c r="DO17">
         <v>12</v>
@@ -9002,8 +9002,8 @@
       <c r="CB18">
         <v>12</v>
       </c>
-      <c r="CC18">
-        <v>12</v>
+      <c r="CC18" s="2">
+        <v>0</v>
       </c>
       <c r="CD18" s="2">
         <v>0</v>
@@ -9062,8 +9062,8 @@
       <c r="CV18" s="2">
         <v>0</v>
       </c>
-      <c r="CW18" s="2">
-        <v>0</v>
+      <c r="CW18" s="5">
+        <v>7</v>
       </c>
       <c r="CX18">
         <v>12</v>
@@ -9077,41 +9077,41 @@
       <c r="DA18">
         <v>12</v>
       </c>
-      <c r="DB18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DE18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DF18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DG18" s="4">
-        <v>5</v>
-      </c>
-      <c r="DH18" s="5">
-        <v>0</v>
-      </c>
-      <c r="DI18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL18" s="3">
-        <v>0</v>
-      </c>
-      <c r="DM18" s="3">
-        <v>0</v>
+      <c r="DB18">
+        <v>12</v>
+      </c>
+      <c r="DC18">
+        <v>12</v>
+      </c>
+      <c r="DD18">
+        <v>12</v>
+      </c>
+      <c r="DE18">
+        <v>12</v>
+      </c>
+      <c r="DF18">
+        <v>12</v>
+      </c>
+      <c r="DG18">
+        <v>12</v>
+      </c>
+      <c r="DH18">
+        <v>12</v>
+      </c>
+      <c r="DI18">
+        <v>12</v>
+      </c>
+      <c r="DJ18">
+        <v>12</v>
+      </c>
+      <c r="DK18">
+        <v>12</v>
+      </c>
+      <c r="DL18">
+        <v>12</v>
+      </c>
+      <c r="DM18">
+        <v>12</v>
       </c>
       <c r="DN18">
         <v>12</v>
@@ -9454,8 +9454,8 @@
       <c r="CB19">
         <v>12</v>
       </c>
-      <c r="CC19">
-        <v>12</v>
+      <c r="CC19" s="2">
+        <v>0</v>
       </c>
       <c r="CD19" s="2">
         <v>0</v>
@@ -9514,11 +9514,11 @@
       <c r="CV19" s="2">
         <v>0</v>
       </c>
-      <c r="CW19" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX19">
-        <v>12</v>
+      <c r="CW19">
+        <v>12</v>
+      </c>
+      <c r="CX19" s="5">
+        <v>0</v>
       </c>
       <c r="CY19">
         <v>12</v>
@@ -9529,20 +9529,20 @@
       <c r="DA19">
         <v>12</v>
       </c>
-      <c r="DB19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DC19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DD19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DE19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DF19" s="3">
-        <v>0</v>
+      <c r="DB19">
+        <v>12</v>
+      </c>
+      <c r="DC19">
+        <v>12</v>
+      </c>
+      <c r="DD19">
+        <v>12</v>
+      </c>
+      <c r="DE19">
+        <v>12</v>
+      </c>
+      <c r="DF19">
+        <v>12</v>
       </c>
       <c r="DG19">
         <v>12</v>
@@ -9550,20 +9550,20 @@
       <c r="DH19">
         <v>12</v>
       </c>
-      <c r="DI19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DJ19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DK19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DL19" s="3">
-        <v>0</v>
-      </c>
-      <c r="DM19" s="3">
-        <v>0</v>
+      <c r="DI19">
+        <v>12</v>
+      </c>
+      <c r="DJ19">
+        <v>12</v>
+      </c>
+      <c r="DK19">
+        <v>12</v>
+      </c>
+      <c r="DL19">
+        <v>12</v>
+      </c>
+      <c r="DM19">
+        <v>12</v>
       </c>
       <c r="DN19">
         <v>12</v>
@@ -9574,8 +9574,8 @@
       <c r="DP19">
         <v>12</v>
       </c>
-      <c r="DQ19">
-        <v>12</v>
+      <c r="DQ19" s="5">
+        <v>0</v>
       </c>
       <c r="DR19" s="2">
         <v>0</v>
@@ -9906,8 +9906,8 @@
       <c r="CB20">
         <v>12</v>
       </c>
-      <c r="CC20">
-        <v>12</v>
+      <c r="CC20" s="2">
+        <v>0</v>
       </c>
       <c r="CD20" s="2">
         <v>0</v>
@@ -9966,14 +9966,14 @@
       <c r="CV20" s="2">
         <v>0</v>
       </c>
-      <c r="CW20" s="2">
-        <v>0</v>
+      <c r="CW20">
+        <v>12</v>
       </c>
       <c r="CX20">
         <v>12</v>
       </c>
-      <c r="CY20">
-        <v>12</v>
+      <c r="CY20" s="4">
+        <v>0</v>
       </c>
       <c r="CZ20">
         <v>12</v>
@@ -9981,20 +9981,20 @@
       <c r="DA20">
         <v>12</v>
       </c>
-      <c r="DB20">
-        <v>12</v>
-      </c>
-      <c r="DC20">
-        <v>12</v>
-      </c>
-      <c r="DD20">
-        <v>12</v>
-      </c>
-      <c r="DE20">
-        <v>12</v>
-      </c>
-      <c r="DF20">
-        <v>12</v>
+      <c r="DB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF20" s="3">
+        <v>0</v>
       </c>
       <c r="DG20">
         <v>12</v>
@@ -10005,26 +10005,26 @@
       <c r="DI20">
         <v>12</v>
       </c>
-      <c r="DJ20">
-        <v>12</v>
-      </c>
-      <c r="DK20">
-        <v>12</v>
-      </c>
-      <c r="DL20">
-        <v>12</v>
-      </c>
-      <c r="DM20">
-        <v>12</v>
-      </c>
-      <c r="DN20">
-        <v>12</v>
+      <c r="DJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="DN20" s="3">
+        <v>0</v>
       </c>
       <c r="DO20">
         <v>12</v>
       </c>
-      <c r="DP20">
-        <v>12</v>
+      <c r="DP20" s="4">
+        <v>6</v>
       </c>
       <c r="DQ20">
         <v>12</v>
@@ -10358,8 +10358,8 @@
       <c r="CB21">
         <v>12</v>
       </c>
-      <c r="CC21">
-        <v>12</v>
+      <c r="CC21" s="2">
+        <v>0</v>
       </c>
       <c r="CD21" s="2">
         <v>0</v>
@@ -10418,8 +10418,8 @@
       <c r="CV21" s="2">
         <v>0</v>
       </c>
-      <c r="CW21" s="2">
-        <v>0</v>
+      <c r="CW21">
+        <v>12</v>
       </c>
       <c r="CX21">
         <v>12</v>
@@ -10427,26 +10427,26 @@
       <c r="CY21">
         <v>12</v>
       </c>
-      <c r="CZ21">
-        <v>12</v>
+      <c r="CZ21" s="5">
+        <v>7</v>
       </c>
       <c r="DA21">
         <v>12</v>
       </c>
-      <c r="DB21">
-        <v>12</v>
-      </c>
-      <c r="DC21">
-        <v>12</v>
-      </c>
-      <c r="DD21">
-        <v>12</v>
-      </c>
-      <c r="DE21">
-        <v>12</v>
-      </c>
-      <c r="DF21">
-        <v>12</v>
+      <c r="DB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DC21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF21" s="3">
+        <v>0</v>
       </c>
       <c r="DG21">
         <v>12</v>
@@ -10457,23 +10457,23 @@
       <c r="DI21">
         <v>12</v>
       </c>
-      <c r="DJ21">
-        <v>12</v>
-      </c>
-      <c r="DK21">
-        <v>12</v>
-      </c>
-      <c r="DL21">
-        <v>12</v>
-      </c>
-      <c r="DM21">
-        <v>12</v>
-      </c>
-      <c r="DN21">
-        <v>12</v>
-      </c>
-      <c r="DO21">
-        <v>12</v>
+      <c r="DJ21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DK21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DL21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DM21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DN21" s="3">
+        <v>0</v>
+      </c>
+      <c r="DO21" s="5">
+        <v>0</v>
       </c>
       <c r="DP21">
         <v>12</v>
@@ -10810,8 +10810,8 @@
       <c r="CB22">
         <v>12</v>
       </c>
-      <c r="CC22">
-        <v>12</v>
+      <c r="CC22" s="2">
+        <v>0</v>
       </c>
       <c r="CD22" s="2">
         <v>0</v>
@@ -10870,8 +10870,8 @@
       <c r="CV22" s="2">
         <v>0</v>
       </c>
-      <c r="CW22" s="2">
-        <v>0</v>
+      <c r="CW22">
+        <v>12</v>
       </c>
       <c r="CX22">
         <v>12</v>
@@ -10882,23 +10882,23 @@
       <c r="CZ22">
         <v>12</v>
       </c>
-      <c r="DA22">
-        <v>12</v>
-      </c>
-      <c r="DB22">
-        <v>12</v>
-      </c>
-      <c r="DC22">
-        <v>12</v>
-      </c>
-      <c r="DD22">
-        <v>12</v>
-      </c>
-      <c r="DE22">
-        <v>12</v>
-      </c>
-      <c r="DF22">
-        <v>12</v>
+      <c r="DA22" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="DC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD22" s="3">
+        <v>8</v>
+      </c>
+      <c r="DE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF22" s="3">
+        <v>0</v>
       </c>
       <c r="DG22">
         <v>12</v>
@@ -10909,20 +10909,20 @@
       <c r="DI22">
         <v>12</v>
       </c>
-      <c r="DJ22">
-        <v>12</v>
-      </c>
-      <c r="DK22">
-        <v>12</v>
-      </c>
-      <c r="DL22">
-        <v>12</v>
-      </c>
-      <c r="DM22">
-        <v>12</v>
-      </c>
-      <c r="DN22">
-        <v>12</v>
+      <c r="DJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="DK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="DL22" s="3">
+        <v>8</v>
+      </c>
+      <c r="DM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="DN22" s="3">
+        <v>0</v>
       </c>
       <c r="DO22">
         <v>12</v>
@@ -11262,8 +11262,8 @@
       <c r="CB23">
         <v>12</v>
       </c>
-      <c r="CC23">
-        <v>12</v>
+      <c r="CC23" s="2">
+        <v>0</v>
       </c>
       <c r="CD23" s="2">
         <v>0</v>
@@ -11322,8 +11322,8 @@
       <c r="CV23" s="2">
         <v>0</v>
       </c>
-      <c r="CW23" s="2">
-        <v>0</v>
+      <c r="CW23">
+        <v>12</v>
       </c>
       <c r="CX23">
         <v>12</v>
@@ -11337,44 +11337,44 @@
       <c r="DA23">
         <v>12</v>
       </c>
-      <c r="DB23">
-        <v>12</v>
-      </c>
-      <c r="DC23">
-        <v>12</v>
-      </c>
-      <c r="DD23">
-        <v>12</v>
-      </c>
-      <c r="DE23">
-        <v>12</v>
-      </c>
-      <c r="DF23">
-        <v>12</v>
-      </c>
-      <c r="DG23">
-        <v>12</v>
-      </c>
-      <c r="DH23">
-        <v>12</v>
-      </c>
-      <c r="DI23">
-        <v>12</v>
-      </c>
-      <c r="DJ23">
-        <v>12</v>
-      </c>
-      <c r="DK23">
-        <v>12</v>
-      </c>
-      <c r="DL23">
-        <v>12</v>
-      </c>
-      <c r="DM23">
-        <v>12</v>
-      </c>
-      <c r="DN23">
-        <v>12</v>
+      <c r="DB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DG23" s="4">
+        <v>0</v>
+      </c>
+      <c r="DH23" s="5">
+        <v>5</v>
+      </c>
+      <c r="DI23" s="5">
+        <v>0</v>
+      </c>
+      <c r="DJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DM23" s="3">
+        <v>0</v>
+      </c>
+      <c r="DN23" s="3">
+        <v>0</v>
       </c>
       <c r="DO23">
         <v>12</v>
@@ -11714,8 +11714,8 @@
       <c r="CB24">
         <v>12</v>
       </c>
-      <c r="CC24">
-        <v>12</v>
+      <c r="CC24" s="2">
+        <v>0</v>
       </c>
       <c r="CD24" s="2">
         <v>0</v>
@@ -11774,8 +11774,8 @@
       <c r="CV24" s="2">
         <v>0</v>
       </c>
-      <c r="CW24" s="2">
-        <v>0</v>
+      <c r="CW24">
+        <v>12</v>
       </c>
       <c r="CX24">
         <v>12</v>
@@ -11789,20 +11789,20 @@
       <c r="DA24">
         <v>12</v>
       </c>
-      <c r="DB24">
-        <v>12</v>
-      </c>
-      <c r="DC24">
-        <v>12</v>
-      </c>
-      <c r="DD24">
-        <v>12</v>
-      </c>
-      <c r="DE24">
-        <v>12</v>
-      </c>
-      <c r="DF24">
-        <v>12</v>
+      <c r="DB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DF24" s="3">
+        <v>0</v>
       </c>
       <c r="DG24">
         <v>12</v>
@@ -11813,20 +11813,20 @@
       <c r="DI24">
         <v>12</v>
       </c>
-      <c r="DJ24">
-        <v>12</v>
-      </c>
-      <c r="DK24">
-        <v>12</v>
-      </c>
-      <c r="DL24">
-        <v>12</v>
-      </c>
-      <c r="DM24">
-        <v>12</v>
-      </c>
-      <c r="DN24">
-        <v>12</v>
+      <c r="DJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="DN24" s="3">
+        <v>0</v>
       </c>
       <c r="DO24">
         <v>12</v>
@@ -12166,8 +12166,8 @@
       <c r="CB25">
         <v>12</v>
       </c>
-      <c r="CC25">
-        <v>12</v>
+      <c r="CC25" s="2">
+        <v>0</v>
       </c>
       <c r="CD25" s="2">
         <v>0</v>
@@ -12226,8 +12226,8 @@
       <c r="CV25" s="2">
         <v>0</v>
       </c>
-      <c r="CW25" s="2">
-        <v>0</v>
+      <c r="CW25">
+        <v>12</v>
       </c>
       <c r="CX25">
         <v>12</v>
@@ -12618,8 +12618,8 @@
       <c r="CB26">
         <v>12</v>
       </c>
-      <c r="CC26">
-        <v>12</v>
+      <c r="CC26" s="2">
+        <v>0</v>
       </c>
       <c r="CD26" s="2">
         <v>0</v>
@@ -12678,8 +12678,8 @@
       <c r="CV26" s="2">
         <v>0</v>
       </c>
-      <c r="CW26" s="2">
-        <v>0</v>
+      <c r="CW26">
+        <v>12</v>
       </c>
       <c r="CX26">
         <v>12</v>
@@ -13070,8 +13070,8 @@
       <c r="CB27">
         <v>12</v>
       </c>
-      <c r="CC27">
-        <v>12</v>
+      <c r="CC27" s="2">
+        <v>0</v>
       </c>
       <c r="CD27" s="2">
         <v>0</v>
@@ -13130,8 +13130,8 @@
       <c r="CV27" s="2">
         <v>0</v>
       </c>
-      <c r="CW27" s="2">
-        <v>0</v>
+      <c r="CW27">
+        <v>12</v>
       </c>
       <c r="CX27">
         <v>12</v>
@@ -26577,7 +26577,7 @@
         <v>12</v>
       </c>
       <c r="BK57" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL57">
         <v>12</v>
@@ -27026,7 +27026,7 @@
         <v>12</v>
       </c>
       <c r="BJ58" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BK58">
         <v>12</v>
@@ -27475,7 +27475,7 @@
         <v>12</v>
       </c>
       <c r="BI59" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BJ59">
         <v>12</v>
@@ -29271,7 +29271,7 @@
         <v>12</v>
       </c>
       <c r="BE63" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF63">
         <v>12</v>
@@ -29720,7 +29720,7 @@
         <v>12</v>
       </c>
       <c r="BD64" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE64">
         <v>12</v>
@@ -30169,7 +30169,7 @@
         <v>12</v>
       </c>
       <c r="BC65" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BD65">
         <v>12</v>
@@ -31901,8 +31901,8 @@
       <c r="AC69">
         <v>12</v>
       </c>
-      <c r="AD69" s="6">
-        <v>0</v>
+      <c r="AD69">
+        <v>12</v>
       </c>
       <c r="AE69">
         <v>12</v>
@@ -31910,8 +31910,8 @@
       <c r="AF69">
         <v>12</v>
       </c>
-      <c r="AG69">
-        <v>12</v>
+      <c r="AG69" s="6">
+        <v>0</v>
       </c>
       <c r="AH69">
         <v>12</v>
@@ -31965,7 +31965,7 @@
         <v>12</v>
       </c>
       <c r="AY69" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AZ69">
         <v>12</v>
@@ -32356,18 +32356,18 @@
       <c r="AD70">
         <v>12</v>
       </c>
-      <c r="AE70" s="6">
+      <c r="AE70">
+        <v>12</v>
+      </c>
+      <c r="AF70">
+        <v>12</v>
+      </c>
+      <c r="AG70">
+        <v>12</v>
+      </c>
+      <c r="AH70" s="6">
         <v>4</v>
       </c>
-      <c r="AF70">
-        <v>12</v>
-      </c>
-      <c r="AG70">
-        <v>12</v>
-      </c>
-      <c r="AH70">
-        <v>12</v>
-      </c>
       <c r="AI70">
         <v>12</v>
       </c>
@@ -32414,7 +32414,7 @@
         <v>12</v>
       </c>
       <c r="AX70" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY70">
         <v>12</v>
@@ -32811,8 +32811,8 @@
       <c r="AE71">
         <v>12</v>
       </c>
-      <c r="AF71" s="6">
-        <v>0</v>
+      <c r="AF71">
+        <v>12</v>
       </c>
       <c r="AG71">
         <v>12</v>
@@ -32820,8 +32820,8 @@
       <c r="AH71">
         <v>12</v>
       </c>
-      <c r="AI71">
-        <v>12</v>
+      <c r="AI71" s="6">
+        <v>0</v>
       </c>
       <c r="AJ71">
         <v>12</v>
@@ -32863,7 +32863,7 @@
         <v>12</v>
       </c>
       <c r="AW71" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX71">
         <v>12</v>
@@ -33266,8 +33266,8 @@
       <c r="AF72">
         <v>12</v>
       </c>
-      <c r="AG72" s="6">
-        <v>0</v>
+      <c r="AG72">
+        <v>12</v>
       </c>
       <c r="AH72">
         <v>12</v>
@@ -33275,8 +33275,8 @@
       <c r="AI72">
         <v>12</v>
       </c>
-      <c r="AJ72">
-        <v>12</v>
+      <c r="AJ72" s="6">
+        <v>0</v>
       </c>
       <c r="AK72">
         <v>12</v>
@@ -33721,17 +33721,17 @@
       <c r="AG73">
         <v>12</v>
       </c>
-      <c r="AH73" s="6">
+      <c r="AH73">
+        <v>12</v>
+      </c>
+      <c r="AI73">
+        <v>12</v>
+      </c>
+      <c r="AJ73">
+        <v>12</v>
+      </c>
+      <c r="AK73" s="6">
         <v>4</v>
-      </c>
-      <c r="AI73">
-        <v>12</v>
-      </c>
-      <c r="AJ73">
-        <v>12</v>
-      </c>
-      <c r="AK73">
-        <v>12</v>
       </c>
       <c r="AL73">
         <v>12</v>
@@ -34176,8 +34176,8 @@
       <c r="AH74">
         <v>12</v>
       </c>
-      <c r="AI74" s="6">
-        <v>0</v>
+      <c r="AI74">
+        <v>12</v>
       </c>
       <c r="AJ74">
         <v>12</v>
@@ -34185,8 +34185,8 @@
       <c r="AK74">
         <v>12</v>
       </c>
-      <c r="AL74">
-        <v>12</v>
+      <c r="AL74" s="6">
+        <v>0</v>
       </c>
       <c r="AM74">
         <v>12</v>
@@ -34631,14 +34631,14 @@
       <c r="AI75">
         <v>12</v>
       </c>
-      <c r="AJ75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK75" s="6">
-        <v>1</v>
-      </c>
-      <c r="AL75" s="6">
-        <v>0</v>
+      <c r="AJ75">
+        <v>12</v>
+      </c>
+      <c r="AK75">
+        <v>12</v>
+      </c>
+      <c r="AL75">
+        <v>12</v>
       </c>
       <c r="AM75" s="6">
         <v>0</v>
@@ -35325,6 +35325,9 @@
       </c>
       <c r="DM76" s="6">
         <v>0</v>
+      </c>
+      <c r="DN76">
+        <v>12</v>
       </c>
       <c r="DO76">
         <v>12</v>
@@ -35775,6 +35778,9 @@
       <c r="DM77" s="6">
         <v>2</v>
       </c>
+      <c r="DN77">
+        <v>12</v>
+      </c>
       <c r="DO77">
         <v>12</v>
       </c>
@@ -36224,6 +36230,9 @@
       <c r="DM78" s="6">
         <v>0</v>
       </c>
+      <c r="DN78">
+        <v>12</v>
+      </c>
       <c r="DO78">
         <v>12</v>
       </c>
@@ -36652,8 +36661,8 @@
       <c r="DF79">
         <v>12</v>
       </c>
-      <c r="DG79" s="6">
-        <v>0</v>
+      <c r="DG79">
+        <v>12</v>
       </c>
       <c r="DH79">
         <v>12</v>
@@ -36672,6 +36681,9 @@
       </c>
       <c r="DM79" s="6">
         <v>0</v>
+      </c>
+      <c r="DN79">
+        <v>12</v>
       </c>
       <c r="DO79">
         <v>12</v>
@@ -37104,8 +37116,8 @@
       <c r="DG80">
         <v>12</v>
       </c>
-      <c r="DH80" s="6">
-        <v>4</v>
+      <c r="DH80">
+        <v>12</v>
       </c>
       <c r="DI80">
         <v>12</v>
@@ -37121,6 +37133,9 @@
       </c>
       <c r="DM80" s="6">
         <v>2</v>
+      </c>
+      <c r="DN80">
+        <v>12</v>
       </c>
       <c r="DO80">
         <v>12</v>
@@ -37556,8 +37571,8 @@
       <c r="DH81">
         <v>12</v>
       </c>
-      <c r="DI81" s="6">
-        <v>0</v>
+      <c r="DI81">
+        <v>12</v>
       </c>
       <c r="DJ81">
         <v>12</v>
@@ -37570,6 +37585,9 @@
       </c>
       <c r="DM81" s="6">
         <v>0</v>
+      </c>
+      <c r="DN81">
+        <v>12</v>
       </c>
       <c r="DO81">
         <v>12</v>
@@ -38002,14 +38020,14 @@
       <c r="DG82">
         <v>12</v>
       </c>
-      <c r="DH82">
-        <v>12</v>
+      <c r="DH82" s="6">
+        <v>0</v>
       </c>
       <c r="DI82">
         <v>12</v>
       </c>
-      <c r="DJ82" s="6">
-        <v>0</v>
+      <c r="DJ82">
+        <v>12</v>
       </c>
       <c r="DK82">
         <v>12</v>
@@ -38019,6 +38037,9 @@
       </c>
       <c r="DM82" s="6">
         <v>0</v>
+      </c>
+      <c r="DN82">
+        <v>12</v>
       </c>
       <c r="DO82">
         <v>12</v>
@@ -38454,20 +38475,23 @@
       <c r="DH83">
         <v>12</v>
       </c>
-      <c r="DI83">
-        <v>12</v>
+      <c r="DI83" s="6">
+        <v>4</v>
       </c>
       <c r="DJ83">
         <v>12</v>
       </c>
-      <c r="DK83" s="6">
-        <v>4</v>
+      <c r="DK83">
+        <v>12</v>
       </c>
       <c r="DL83">
         <v>12</v>
       </c>
       <c r="DM83" s="6">
         <v>2</v>
+      </c>
+      <c r="DN83">
+        <v>12</v>
       </c>
       <c r="DO83">
         <v>12</v>
@@ -38906,17 +38930,20 @@
       <c r="DI84">
         <v>12</v>
       </c>
-      <c r="DJ84">
-        <v>12</v>
+      <c r="DJ84" s="6">
+        <v>0</v>
       </c>
       <c r="DK84">
         <v>12</v>
       </c>
-      <c r="DL84" s="6">
-        <v>0</v>
+      <c r="DL84">
+        <v>12</v>
       </c>
       <c r="DM84" s="6">
         <v>0</v>
+      </c>
+      <c r="DN84">
+        <v>12</v>
       </c>
       <c r="DO84">
         <v>12</v>
@@ -39358,14 +39385,14 @@
       <c r="DJ85">
         <v>12</v>
       </c>
-      <c r="DK85">
-        <v>12</v>
+      <c r="DK85" s="6">
+        <v>0</v>
       </c>
       <c r="DL85">
         <v>12</v>
       </c>
-      <c r="DM85">
-        <v>12</v>
+      <c r="DM85" s="6">
+        <v>2</v>
       </c>
       <c r="DN85">
         <v>12</v>
@@ -39813,11 +39840,11 @@
       <c r="DK86">
         <v>12</v>
       </c>
-      <c r="DL86">
-        <v>12</v>
-      </c>
-      <c r="DM86">
-        <v>12</v>
+      <c r="DL86" s="6">
+        <v>4</v>
+      </c>
+      <c r="DM86" s="6">
+        <v>0</v>
       </c>
       <c r="DN86">
         <v>12</v>
@@ -40268,8 +40295,8 @@
       <c r="DL87">
         <v>12</v>
       </c>
-      <c r="DM87">
-        <v>12</v>
+      <c r="DM87" s="6">
+        <v>0</v>
       </c>
       <c r="DN87">
         <v>12</v>
@@ -40442,7 +40469,7 @@
         <v>12</v>
       </c>
       <c r="X88" s="4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y88">
         <v>12</v>
@@ -40897,7 +40924,7 @@
         <v>12</v>
       </c>
       <c r="Y89" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z89">
         <v>12</v>
@@ -41352,7 +41379,7 @@
         <v>12</v>
       </c>
       <c r="Z90" s="4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA90" s="2">
         <v>0</v>
@@ -44546,7 +44573,7 @@
         <v>0</v>
       </c>
       <c r="AJ97" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK97" s="2">
         <v>0</v>
@@ -44998,7 +45025,7 @@
         <v>0</v>
       </c>
       <c r="AJ98" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AK98" s="2">
         <v>0</v>
@@ -52931,7 +52958,7 @@
         <v>12</v>
       </c>
       <c r="DO115" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DP115">
         <v>12</v>
@@ -53380,7 +53407,7 @@
         <v>12</v>
       </c>
       <c r="DN116" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DO116">
         <v>12</v>
@@ -53829,7 +53856,7 @@
         <v>12</v>
       </c>
       <c r="DM117" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DN117">
         <v>12</v>
